--- a/shipClassTests/testResults/system_with_subsystems_test.xlsx
+++ b/shipClassTests/testResults/system_with_subsystems_test.xlsx
@@ -486,7 +486,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -523,10 +523,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -543,10 +543,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -563,10 +563,10 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -580,13 +580,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -600,13 +600,13 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -620,19 +620,19 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4">
         <v>1</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4">
-        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -640,13 +640,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -660,13 +660,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -680,13 +680,13 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -700,19 +700,19 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -720,16 +720,16 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4">
         <v>2</v>
@@ -746,13 +746,13 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4">
         <v>1</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -806,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -826,13 +826,13 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -866,13 +866,13 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -886,13 +886,13 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -906,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -926,13 +926,13 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -946,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -966,13 +966,13 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -986,13 +986,13 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1006,13 +1006,13 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1026,13 +1026,13 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1066,13 +1066,13 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1109,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1149,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1209,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1229,10 +1229,10 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1272,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1617,7 +1617,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1633,7 +1633,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1641,7 +1641,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1649,7 +1649,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1657,7 +1657,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1665,7 +1665,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1673,7 +1673,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1681,7 +1681,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2014,7 +2014,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2046,7 +2046,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2062,7 +2062,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2070,7 +2070,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2078,7 +2078,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2086,7 +2086,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2094,7 +2094,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2102,7 +2102,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2110,7 +2110,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2118,7 +2118,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2126,7 +2126,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2134,7 +2134,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2142,7 +2142,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2150,7 +2150,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2158,7 +2158,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2166,7 +2166,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2174,7 +2174,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2182,7 +2182,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2190,7 +2190,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2198,7 +2198,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2206,7 +2206,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2214,7 +2214,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2222,7 +2222,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2230,7 +2230,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2238,7 +2238,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2246,7 +2246,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2254,7 +2254,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2262,7 +2262,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2270,7 +2270,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2278,7 +2278,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2286,7 +2286,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2294,7 +2294,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2302,7 +2302,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2310,7 +2310,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2318,7 +2318,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2326,7 +2326,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2334,7 +2334,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2342,7 +2342,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2350,7 +2350,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2439,10 +2439,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -2456,10 +2456,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -2473,10 +2473,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -2490,10 +2490,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -2507,16 +2507,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2533,7 +2533,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2550,7 +2550,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2567,7 +2567,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2584,7 +2584,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2601,7 +2601,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2618,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2635,7 +2635,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2666,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2683,10 +2683,10 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2700,10 +2700,10 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2717,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2751,10 +2751,10 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2768,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2785,10 +2785,10 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2802,10 +2802,10 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2819,10 +2819,10 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3308,7 +3308,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3316,7 +3316,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3324,7 +3324,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3332,7 +3332,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3761,7 +3761,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3825,7 +3825,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3833,7 +3833,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3841,7 +3841,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3849,7 +3849,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3857,7 +3857,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3865,7 +3865,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3873,7 +3873,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3881,7 +3881,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3889,7 +3889,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3897,7 +3897,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3905,7 +3905,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3913,7 +3913,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3921,7 +3921,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3929,7 +3929,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3937,7 +3937,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3945,7 +3945,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3953,7 +3953,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3961,7 +3961,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3969,7 +3969,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3977,7 +3977,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3985,7 +3985,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3993,7 +3993,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4001,7 +4001,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4009,7 +4009,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4017,7 +4017,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4025,7 +4025,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4033,7 +4033,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4041,7 +4041,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4049,7 +4049,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4057,7 +4057,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4065,7 +4065,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4073,7 +4073,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -4081,7 +4081,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -4089,7 +4089,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -4097,7 +4097,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -4105,7 +4105,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4190,7 +4190,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4198,7 +4198,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4206,7 +4206,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4214,7 +4214,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4222,7 +4222,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4230,7 +4230,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4238,7 +4238,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4246,7 +4246,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4254,7 +4254,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4262,7 +4262,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4270,7 +4270,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4278,7 +4278,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4286,7 +4286,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4294,7 +4294,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4302,7 +4302,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4310,7 +4310,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4318,7 +4318,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4326,7 +4326,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4334,7 +4334,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4589,13 +4589,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4">
         <v>2</v>
@@ -4623,16 +4623,16 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4640,13 +4640,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
@@ -4657,13 +4657,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
@@ -4674,13 +4674,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
@@ -4691,16 +4691,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4708,16 +4708,16 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4725,16 +4725,16 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4742,13 +4742,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
@@ -4759,13 +4759,13 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -4776,13 +4776,13 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="4">
         <v>2</v>
@@ -4793,13 +4793,13 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4">
         <v>2</v>
@@ -4810,13 +4810,13 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4">
         <v>2</v>
@@ -4827,16 +4827,16 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4844,16 +4844,16 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4861,16 +4861,16 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4878,16 +4878,16 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4895,16 +4895,16 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4912,16 +4912,16 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4929,16 +4929,16 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -4946,16 +4946,16 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -4963,16 +4963,16 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -4980,16 +4980,16 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4997,16 +4997,16 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5014,16 +5014,16 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5031,16 +5031,16 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5048,16 +5048,16 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5065,16 +5065,16 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5082,16 +5082,16 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -5187,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -5221,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -5255,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5524,7 +5524,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -5532,7 +5532,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5540,7 +5540,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -5548,7 +5548,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -5556,7 +5556,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -5564,7 +5564,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -5572,7 +5572,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -5580,7 +5580,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5588,7 +5588,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5596,7 +5596,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5604,7 +5604,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -5612,7 +5612,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5620,7 +5620,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5628,7 +5628,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5636,7 +5636,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -5644,7 +5644,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -5652,7 +5652,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -5660,7 +5660,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -5668,7 +5668,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -5676,7 +5676,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -5684,7 +5684,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5692,7 +5692,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -5700,7 +5700,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5708,7 +5708,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5716,7 +5716,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5724,7 +5724,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5732,7 +5732,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5740,7 +5740,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5748,7 +5748,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5756,7 +5756,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5764,7 +5764,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5772,7 +5772,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5780,7 +5780,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5897,7 +5897,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5913,7 +5913,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5921,7 +5921,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5929,7 +5929,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5937,7 +5937,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5945,7 +5945,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5953,7 +5953,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -5961,7 +5961,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5969,7 +5969,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -5977,7 +5977,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -5985,7 +5985,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -5993,7 +5993,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6001,7 +6001,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6009,7 +6009,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6017,7 +6017,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6025,7 +6025,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6033,7 +6033,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6041,7 +6041,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6049,7 +6049,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6057,7 +6057,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6065,7 +6065,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6073,7 +6073,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6081,7 +6081,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6089,7 +6089,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6097,7 +6097,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6105,7 +6105,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6113,7 +6113,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6121,7 +6121,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6129,7 +6129,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6137,7 +6137,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6342,7 +6342,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6382,7 +6382,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6390,7 +6390,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6438,7 +6438,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6446,7 +6446,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6454,7 +6454,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6462,7 +6462,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6470,7 +6470,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6478,7 +6478,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6486,7 +6486,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6494,7 +6494,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6502,7 +6502,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6510,7 +6510,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6518,7 +6518,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6526,7 +6526,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6542,7 +6542,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6550,7 +6550,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6558,7 +6558,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">

--- a/shipClassTests/testResults/system_with_subsystems_test.xlsx
+++ b/shipClassTests/testResults/system_with_subsystems_test.xlsx
@@ -486,7 +486,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -506,7 +506,7 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -580,10 +580,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -600,10 +600,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -620,10 +620,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -640,10 +640,10 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -660,10 +660,10 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -700,19 +700,19 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -763,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1172,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1617,7 +1617,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2014,7 +2014,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2046,7 +2046,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2070,7 +2070,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2222,7 +2222,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2230,7 +2230,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2238,7 +2238,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2246,7 +2246,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2286,7 +2286,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2318,7 +2318,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2490,13 +2490,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
@@ -2507,13 +2507,13 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="4">
         <v>2</v>
@@ -2524,13 +2524,13 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -2541,13 +2541,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
@@ -2558,13 +2558,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
@@ -2575,10 +2575,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -2592,10 +2592,10 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -2609,10 +2609,10 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2626,10 +2626,10 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2643,10 +2643,10 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2660,10 +2660,10 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="4">
         <v>2</v>
@@ -2751,10 +2751,10 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2768,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4">
         <v>2</v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
@@ -2836,10 +2836,10 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2853,10 +2853,10 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2870,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2887,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2904,10 +2904,10 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2938,10 +2938,10 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3348,7 +3348,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3356,7 +3356,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3364,7 +3364,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3372,7 +3372,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3380,7 +3380,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3388,7 +3388,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3396,7 +3396,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3404,7 +3404,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3753,7 +3753,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3761,7 +3761,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3769,7 +3769,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3777,7 +3777,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3785,7 +3785,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3841,7 +3841,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3873,7 +3873,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3881,7 +3881,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3889,7 +3889,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3897,7 +3897,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3905,7 +3905,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3913,7 +3913,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3921,7 +3921,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3929,7 +3929,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3937,7 +3937,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3945,7 +3945,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3953,7 +3953,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3961,7 +3961,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3969,7 +3969,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3977,7 +3977,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3985,7 +3985,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3993,7 +3993,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4001,7 +4001,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4009,7 +4009,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4017,7 +4017,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4025,7 +4025,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4033,7 +4033,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4041,7 +4041,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4049,7 +4049,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4057,7 +4057,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4065,7 +4065,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4073,7 +4073,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -4081,7 +4081,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -4089,7 +4089,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -4097,7 +4097,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -4105,7 +4105,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4302,7 +4302,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4310,7 +4310,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4342,7 +4342,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4350,7 +4350,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4358,7 +4358,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4366,7 +4366,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4374,7 +4374,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4382,7 +4382,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4390,7 +4390,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4589,16 +4589,16 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4606,16 +4606,16 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4626,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4646,10 +4646,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4663,10 +4663,10 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4677,13 +4677,13 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4714,10 +4714,10 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4731,10 +4731,10 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4748,10 +4748,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4782,10 +4782,10 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4799,10 +4799,10 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4816,10 +4816,10 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -4850,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -4901,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -4935,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -4986,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -5020,7 +5020,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -5122,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -5156,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -5173,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -5309,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -5377,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -5394,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -5411,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -5428,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5484,7 +5484,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5508,7 +5508,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5897,7 +5897,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5913,7 +5913,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5921,7 +5921,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5929,7 +5929,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5937,7 +5937,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5945,7 +5945,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5953,7 +5953,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -5961,7 +5961,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5969,7 +5969,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -5977,7 +5977,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -5985,7 +5985,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -5993,7 +5993,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6001,7 +6001,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6009,7 +6009,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6017,7 +6017,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6025,7 +6025,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6033,7 +6033,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6041,7 +6041,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6049,7 +6049,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6057,7 +6057,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6065,7 +6065,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6073,7 +6073,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6081,7 +6081,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6089,7 +6089,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6097,7 +6097,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6105,7 +6105,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6113,7 +6113,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6121,7 +6121,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6129,7 +6129,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6137,7 +6137,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6145,7 +6145,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6153,7 +6153,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6161,7 +6161,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6169,7 +6169,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6177,7 +6177,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6185,7 +6185,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6193,7 +6193,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6201,7 +6201,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6209,7 +6209,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6217,7 +6217,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6225,7 +6225,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6233,7 +6233,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6241,7 +6241,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6249,7 +6249,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6257,7 +6257,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6265,7 +6265,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6273,7 +6273,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6281,7 +6281,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6289,7 +6289,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6326,7 +6326,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6334,7 +6334,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6342,7 +6342,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6350,7 +6350,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6358,7 +6358,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6366,7 +6366,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6382,7 +6382,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6390,7 +6390,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6398,7 +6398,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6406,7 +6406,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6414,7 +6414,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6422,7 +6422,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6430,7 +6430,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/shipClassTests/testResults/system_with_subsystems_test.xlsx
+++ b/shipClassTests/testResults/system_with_subsystems_test.xlsx
@@ -407,7 +407,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -415,7 +415,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -423,7 +423,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -431,7 +431,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -439,7 +439,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -447,7 +447,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -455,7 +455,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -463,7 +463,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -471,7 +471,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -479,7 +479,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -487,7 +487,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -495,7 +495,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -503,7 +503,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -511,7 +511,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -519,7 +519,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -527,7 +527,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -535,7 +535,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -559,7 +559,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -567,7 +567,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -575,7 +575,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -583,7 +583,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -591,7 +591,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -599,7 +599,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -607,7 +607,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -615,7 +615,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -623,7 +623,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -631,7 +631,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -639,7 +639,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -647,7 +647,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -655,7 +655,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -663,7 +663,7 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -671,7 +671,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -679,7 +679,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -687,7 +687,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -695,7 +695,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -703,7 +703,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -711,7 +711,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -719,7 +719,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -727,7 +727,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -735,7 +735,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -743,7 +743,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -751,7 +751,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -759,7 +759,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -775,7 +775,7 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -783,7 +783,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -791,7 +791,7 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -799,7 +799,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -841,7 +841,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -849,7 +849,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -857,7 +857,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -865,7 +865,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -873,7 +873,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -889,7 +889,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -905,7 +905,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -921,7 +921,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -937,7 +937,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -945,7 +945,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -953,7 +953,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -961,7 +961,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -985,7 +985,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -993,7 +993,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1001,7 +1001,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1009,7 +1009,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1017,7 +1017,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1025,7 +1025,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1033,7 +1033,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1041,7 +1041,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1049,7 +1049,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1057,7 +1057,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1065,7 +1065,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1073,7 +1073,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1081,7 +1081,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1089,7 +1089,7 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1105,7 +1105,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1113,7 +1113,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1129,7 +1129,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1137,7 +1137,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1145,7 +1145,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1153,7 +1153,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1161,7 +1161,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1169,7 +1169,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1177,7 +1177,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1185,7 +1185,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1209,7 +1209,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1217,7 +1217,7 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1225,7 +1225,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1259,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1323,7 +1323,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1331,7 +1331,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1339,7 +1339,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1379,7 +1379,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1395,7 +1395,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1403,7 +1403,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1443,7 +1443,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1523,7 +1523,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1531,7 +1531,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1539,7 +1539,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1579,7 +1579,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1619,7 +1619,7 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1635,7 +1635,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1733,7 +1733,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1805,7 +1805,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1813,7 +1813,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1821,7 +1821,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1901,7 +1901,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1949,7 +1949,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1973,7 +1973,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2111,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2119,7 +2119,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2127,7 +2127,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2135,7 +2135,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2143,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2151,7 +2151,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2159,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2167,7 +2167,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2175,7 +2175,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2183,7 +2183,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2191,7 +2191,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2199,7 +2199,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2207,7 +2207,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2215,7 +2215,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2223,7 +2223,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2231,7 +2231,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2239,7 +2239,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2247,7 +2247,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2255,7 +2255,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2263,7 +2263,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2271,7 +2271,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2279,7 +2279,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2287,7 +2287,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2295,7 +2295,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2303,7 +2303,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2311,7 +2311,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2319,7 +2319,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2327,7 +2327,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2335,7 +2335,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2343,7 +2343,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2351,7 +2351,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2359,7 +2359,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2367,7 +2367,7 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2375,7 +2375,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2383,7 +2383,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2391,7 +2391,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2399,7 +2399,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2407,7 +2407,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2415,7 +2415,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2423,7 +2423,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2431,7 +2431,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2439,7 +2439,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2447,7 +2447,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2455,7 +2455,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2463,7 +2463,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2471,7 +2471,7 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2487,7 +2487,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2495,7 +2495,7 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2503,7 +2503,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2545,7 +2545,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2553,7 +2553,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2561,7 +2561,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2569,7 +2569,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2585,7 +2585,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2593,7 +2593,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2601,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2609,7 +2609,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2617,7 +2617,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2625,7 +2625,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2633,7 +2633,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2641,7 +2641,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2649,7 +2649,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2657,7 +2657,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2689,7 +2689,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2705,7 +2705,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2713,7 +2713,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2721,7 +2721,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2729,7 +2729,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2753,7 +2753,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2801,7 +2801,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2809,7 +2809,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2817,7 +2817,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2825,7 +2825,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2833,7 +2833,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2841,7 +2841,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2849,7 +2849,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2857,7 +2857,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2865,7 +2865,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2873,7 +2873,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2881,7 +2881,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2889,7 +2889,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2905,7 +2905,7 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2913,7 +2913,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2929,7 +2929,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3011,7 +3011,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3019,7 +3019,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3027,7 +3027,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3035,7 +3035,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3043,7 +3043,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3051,7 +3051,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3083,7 +3083,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3091,7 +3091,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3107,7 +3107,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3115,7 +3115,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3123,7 +3123,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3131,7 +3131,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3139,7 +3139,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3147,7 +3147,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3155,7 +3155,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3171,7 +3171,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3179,7 +3179,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3187,7 +3187,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3195,7 +3195,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3203,7 +3203,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3211,7 +3211,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3219,7 +3219,7 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3227,7 +3227,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3235,7 +3235,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3243,7 +3243,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3251,7 +3251,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3259,7 +3259,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3267,7 +3267,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3275,7 +3275,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3283,7 +3283,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3291,7 +3291,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3299,7 +3299,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3307,7 +3307,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3315,7 +3315,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3323,7 +3323,7 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3331,7 +3331,7 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3339,7 +3339,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3347,7 +3347,7 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3355,7 +3355,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3389,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3397,7 +3397,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3413,7 +3413,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3421,7 +3421,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3429,7 +3429,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3437,7 +3437,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3445,7 +3445,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3453,7 +3453,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3461,7 +3461,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3469,7 +3469,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3477,7 +3477,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3485,7 +3485,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3493,7 +3493,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3501,7 +3501,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3509,7 +3509,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3517,7 +3517,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3525,7 +3525,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3533,7 +3533,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3541,7 +3541,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3549,7 +3549,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3557,7 +3557,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3565,7 +3565,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3573,7 +3573,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3581,7 +3581,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3589,7 +3589,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3597,7 +3597,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3605,7 +3605,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3613,7 +3613,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3621,7 +3621,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3629,7 +3629,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3637,7 +3637,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3645,7 +3645,7 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3653,7 +3653,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3661,7 +3661,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3669,7 +3669,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3677,7 +3677,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3685,7 +3685,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3693,7 +3693,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3701,7 +3701,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3709,7 +3709,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3717,7 +3717,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3725,7 +3725,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3733,7 +3733,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3741,7 +3741,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3749,7 +3749,7 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3757,7 +3757,7 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3765,7 +3765,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3781,7 +3781,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3823,7 +3823,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3831,7 +3831,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3839,7 +3839,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3847,7 +3847,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3855,7 +3855,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3911,7 +3911,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3919,7 +3919,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3927,7 +3927,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3935,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3967,7 +3967,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3983,7 +3983,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3991,7 +3991,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3999,7 +3999,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4007,7 +4007,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4015,7 +4015,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4031,7 +4031,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4079,7 +4079,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4087,7 +4087,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4095,7 +4095,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4103,7 +4103,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4111,7 +4111,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4119,7 +4119,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4127,7 +4127,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4135,7 +4135,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4143,7 +4143,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4151,7 +4151,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4159,7 +4159,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4167,7 +4167,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4183,7 +4183,7 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -4191,7 +4191,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -4199,7 +4199,7 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -4207,7 +4207,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
